--- a/final_data_pipeline/output/325120_elec_options.xlsx
+++ b/final_data_pipeline/output/325120_elec_options.xlsx
@@ -3867,7 +3867,7 @@
         <v>137</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE32">
         <v>8000</v>
@@ -3965,7 +3965,7 @@
         <v>137</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE33">
         <v>8000</v>
@@ -4060,7 +4060,7 @@
         <v>137</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE34">
         <v>8000</v>
@@ -6459,7 +6459,7 @@
         <v>137</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6554,7 +6554,7 @@
         <v>137</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -6652,7 +6652,7 @@
         <v>137</v>
       </c>
       <c r="AD61">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE61">
         <v>8000</v>
@@ -6747,7 +6747,7 @@
         <v>137</v>
       </c>
       <c r="AD62">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE62">
         <v>8000</v>
@@ -6842,7 +6842,7 @@
         <v>137</v>
       </c>
       <c r="AD63">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE63">
         <v>8000</v>
@@ -6937,7 +6937,7 @@
         <v>137</v>
       </c>
       <c r="AD64">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE64">
         <v>8000</v>
@@ -7032,7 +7032,7 @@
         <v>137</v>
       </c>
       <c r="AD65">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE65">
         <v>8000</v>
@@ -7130,7 +7130,7 @@
         <v>137</v>
       </c>
       <c r="AD66">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE66">
         <v>8000</v>
@@ -7228,7 +7228,7 @@
         <v>137</v>
       </c>
       <c r="AD67">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE67">
         <v>8000</v>
@@ -7611,7 +7611,7 @@
         <v>137</v>
       </c>
       <c r="AD71">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE71">
         <v>8000</v>
@@ -7706,7 +7706,7 @@
         <v>137</v>
       </c>
       <c r="AD72">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE72">
         <v>8000</v>
@@ -7804,7 +7804,7 @@
         <v>137</v>
       </c>
       <c r="AD73">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AE73">
         <v>8000</v>
@@ -7902,7 +7902,7 @@
         <v>137</v>
       </c>
       <c r="AD74">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE74">
         <v>8000</v>
@@ -7997,7 +7997,7 @@
         <v>137</v>
       </c>
       <c r="AD75">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE75">
         <v>8000</v>
@@ -8092,7 +8092,7 @@
         <v>137</v>
       </c>
       <c r="AD76">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE76">
         <v>8000</v>
@@ -11934,7 +11934,7 @@
         <v>137</v>
       </c>
       <c r="AD116">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE116">
         <v>8000</v>
@@ -12029,7 +12029,7 @@
         <v>137</v>
       </c>
       <c r="AD117">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE117">
         <v>8000</v>
@@ -12124,7 +12124,7 @@
         <v>137</v>
       </c>
       <c r="AD118">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE118">
         <v>8000</v>
@@ -12795,7 +12795,7 @@
         <v>137</v>
       </c>
       <c r="AD125">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE125">
         <v>8000</v>
@@ -12890,7 +12890,7 @@
         <v>137</v>
       </c>
       <c r="AD126">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE126">
         <v>8000</v>
@@ -12988,7 +12988,7 @@
         <v>137</v>
       </c>
       <c r="AD127">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE127">
         <v>8000</v>
@@ -13086,7 +13086,7 @@
         <v>137</v>
       </c>
       <c r="AD128">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE128">
         <v>8000</v>
@@ -13181,7 +13181,7 @@
         <v>137</v>
       </c>
       <c r="AD129">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE129">
         <v>8000</v>
@@ -13276,7 +13276,7 @@
         <v>137</v>
       </c>
       <c r="AD130">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AE130">
         <v>8000</v>
@@ -13371,7 +13371,7 @@
         <v>137</v>
       </c>
       <c r="AD131">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE131">
         <v>8000</v>
@@ -13469,7 +13469,7 @@
         <v>137</v>
       </c>
       <c r="AD132">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE132">
         <v>8000</v>
@@ -13564,7 +13564,7 @@
         <v>137</v>
       </c>
       <c r="AD133">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE133">
         <v>8000</v>
